--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB TABERNES BLANQUES - FERNANDO GIL.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB TABERNES BLANQUES - FERNANDO GIL.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. VIDAL BALDOVI</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>32.4674</v>
+        <v>40.3728</v>
       </c>
       <c r="E2" t="n">
-        <v>11.3183</v>
+        <v>27.9527</v>
       </c>
       <c r="F2" t="n">
-        <v>21.1491</v>
+        <v>12.42</v>
       </c>
       <c r="G2" t="n">
-        <v>17.2565</v>
+        <v>34.3824</v>
       </c>
       <c r="H2" t="n">
-        <v>26.2582</v>
+        <v>28.3014</v>
       </c>
       <c r="I2" t="n">
-        <v>-9.001799999999999</v>
+        <v>6.081000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>55.3641</v>
+        <v>71.1332</v>
       </c>
       <c r="K2" t="n">
-        <v>48.23</v>
+        <v>49.1405</v>
       </c>
       <c r="L2" t="n">
-        <v>7.133799999999999</v>
+        <v>21.9926</v>
       </c>
       <c r="M2" t="n">
-        <v>-38.1075</v>
+        <v>-36.7506</v>
       </c>
       <c r="N2" t="n">
-        <v>-21.9715</v>
+        <v>-20.8393</v>
       </c>
       <c r="O2" t="n">
-        <v>-16.1359</v>
+        <v>-15.9115</v>
       </c>
       <c r="P2" t="n">
-        <v>-6.047800000000001</v>
+        <v>-21.2579</v>
       </c>
       <c r="Q2" t="n">
-        <v>-66.5226</v>
+        <v>-85.7645</v>
       </c>
       <c r="R2" t="n">
-        <v>60.4749</v>
+        <v>64.5065</v>
       </c>
       <c r="S2" t="n">
-        <v>8.8255</v>
+        <v>-4.9272</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.7</v>
+        <v>-7.7218</v>
       </c>
       <c r="U2" t="n">
-        <v>10.5257</v>
+        <v>2.7941</v>
       </c>
       <c r="V2" t="n">
-        <v>12.4329</v>
+        <v>32.1754</v>
       </c>
       <c r="W2" t="n">
-        <v>24.1764</v>
+        <v>50.3053</v>
       </c>
       <c r="X2" t="n">
-        <v>-11.7434</v>
+        <v>-18.1305</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>S. VIDAL BALDOVI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7427</v>
+        <v>25.8314</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6865</v>
+        <v>7.941800000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>9.056000000000001</v>
+        <v>17.8896</v>
       </c>
       <c r="G3" t="n">
-        <v>34.3824</v>
+        <v>17.2565</v>
       </c>
       <c r="H3" t="n">
-        <v>28.3014</v>
+        <v>26.2582</v>
       </c>
       <c r="I3" t="n">
-        <v>6.081000000000001</v>
+        <v>-9.001799999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>71.1332</v>
+        <v>55.3641</v>
       </c>
       <c r="K3" t="n">
-        <v>49.1405</v>
+        <v>48.23</v>
       </c>
       <c r="L3" t="n">
-        <v>21.9926</v>
+        <v>7.133799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-36.7506</v>
+        <v>-38.1075</v>
       </c>
       <c r="N3" t="n">
-        <v>-20.8393</v>
+        <v>-21.9715</v>
       </c>
       <c r="O3" t="n">
-        <v>-15.9115</v>
+        <v>-16.1359</v>
       </c>
       <c r="P3" t="n">
-        <v>-21.2579</v>
+        <v>-6.047800000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-85.7645</v>
+        <v>-66.5226</v>
       </c>
       <c r="R3" t="n">
-        <v>64.5065</v>
+        <v>60.4749</v>
       </c>
       <c r="S3" t="n">
-        <v>-19.5571</v>
+        <v>2.1895</v>
       </c>
       <c r="T3" t="n">
-        <v>-18.9882</v>
+        <v>-5.0765</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5692000000000002</v>
+        <v>7.2659</v>
       </c>
       <c r="V3" t="n">
-        <v>32.1754</v>
+        <v>12.4329</v>
       </c>
       <c r="W3" t="n">
-        <v>50.3053</v>
+        <v>24.1764</v>
       </c>
       <c r="X3" t="n">
-        <v>-18.1305</v>
+        <v>-11.7434</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>23.4416</v>
+        <v>18.4469</v>
       </c>
       <c r="E4" t="n">
-        <v>15.6751</v>
+        <v>7.3057</v>
       </c>
       <c r="F4" t="n">
-        <v>7.766699999999999</v>
+        <v>11.1414</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04319999999999921</v>
+        <v>18.4823</v>
       </c>
       <c r="H4" t="n">
-        <v>3.373200000000001</v>
+        <v>19.5554</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.3303</v>
+        <v>-1.0732</v>
       </c>
       <c r="J4" t="n">
-        <v>31.5278</v>
+        <v>27.6564</v>
       </c>
       <c r="K4" t="n">
-        <v>21.6413</v>
+        <v>25.2939</v>
       </c>
       <c r="L4" t="n">
-        <v>9.8865</v>
+        <v>2.3625</v>
       </c>
       <c r="M4" t="n">
-        <v>-31.485</v>
+        <v>-9.173999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-18.2683</v>
+        <v>-5.7384</v>
       </c>
       <c r="O4" t="n">
-        <v>-13.2171</v>
+        <v>-3.4358</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.8799</v>
+        <v>-8.0634</v>
       </c>
       <c r="Q4" t="n">
-        <v>-60.1083</v>
+        <v>-38.8509</v>
       </c>
       <c r="R4" t="n">
-        <v>52.2284</v>
+        <v>30.787</v>
       </c>
       <c r="S4" t="n">
-        <v>25.9367</v>
+        <v>1.9132</v>
       </c>
       <c r="T4" t="n">
-        <v>14.9796</v>
+        <v>0.9071</v>
       </c>
       <c r="U4" t="n">
-        <v>10.9571</v>
+        <v>1.0057</v>
       </c>
       <c r="V4" t="n">
-        <v>5.341900000000001</v>
+        <v>6.1148</v>
       </c>
       <c r="W4" t="n">
-        <v>29.2757</v>
+        <v>17.5925</v>
       </c>
       <c r="X4" t="n">
-        <v>-23.9339</v>
+        <v>-11.4774</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>18.7856</v>
+        <v>12.2033</v>
       </c>
       <c r="E5" t="n">
-        <v>10.5046</v>
+        <v>12.2033</v>
       </c>
       <c r="F5" t="n">
-        <v>8.2812</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>18.4823</v>
+        <v>12.2033</v>
       </c>
       <c r="H5" t="n">
-        <v>19.5554</v>
+        <v>8.4526</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0732</v>
+        <v>3.7506</v>
       </c>
       <c r="J5" t="n">
-        <v>27.6564</v>
+        <v>12.2033</v>
       </c>
       <c r="K5" t="n">
-        <v>25.2939</v>
+        <v>8.4526</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3625</v>
+        <v>3.7506</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.173999999999999</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.7384</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.4358</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.0634</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-38.8509</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>30.787</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.251600000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.1059</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.8543</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>6.1148</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>17.5925</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.4774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>12.2033</v>
+        <v>6.880400000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2033</v>
+        <v>5.563099999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.3171</v>
       </c>
       <c r="G6" t="n">
-        <v>12.2033</v>
+        <v>22.2772</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4526</v>
+        <v>-5.036600000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7506</v>
+        <v>27.3138</v>
       </c>
       <c r="J6" t="n">
-        <v>12.2033</v>
+        <v>37.9417</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4526</v>
+        <v>7.4172</v>
       </c>
       <c r="L6" t="n">
-        <v>3.7506</v>
+        <v>30.5244</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-15.6643</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-12.4536</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-3.2106</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-6.7803</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-36.2852</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>29.5043</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-4.1486</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-5.3157</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-4.4677</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>9.222</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-13.6897</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SEMEN</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5139</v>
+        <v>6.832</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5866</v>
+        <v>3.177099999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9273</v>
+        <v>3.6552</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1292</v>
+        <v>0.04319999999999921</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7351</v>
+        <v>3.373200000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3942</v>
+        <v>-3.3303</v>
       </c>
       <c r="J7" t="n">
-        <v>1.082</v>
+        <v>31.5278</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0404</v>
+        <v>21.6413</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0417</v>
+        <v>9.8865</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0472</v>
+        <v>-31.485</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3053</v>
+        <v>-18.2683</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3525</v>
+        <v>-13.2171</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1833</v>
+        <v>-7.8799</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>-60.1083</v>
       </c>
       <c r="R7" t="n">
-        <v>0.733</v>
+        <v>52.2284</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5679</v>
+        <v>9.327299999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4208</v>
+        <v>2.4821</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1471</v>
+        <v>6.8455</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.341900000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>29.2757</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-23.9339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VILLARROYA FELIPO</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0864</v>
+        <v>5.0337</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4683</v>
+        <v>6.453900000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6181</v>
+        <v>-1.420600000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9142</v>
+        <v>5.012100000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0007</v>
+        <v>8.493400000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-3.4814</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4502</v>
+        <v>20.0508</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0496</v>
+        <v>18.5576</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5994</v>
+        <v>1.4932</v>
       </c>
       <c r="M8" t="n">
-        <v>0.464</v>
+        <v>-15.0389</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0489</v>
+        <v>-10.0639</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5128</v>
+        <v>-4.9748</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>8.246499999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-27.6721</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>35.9185</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1722</v>
+        <v>-3.5458</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0181</v>
+        <v>-2.5416</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1541</v>
+        <v>-1.0043</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-4.6797</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>16.6159</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-21.2957</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1528999999999998</v>
+        <v>1.8925</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1885</v>
+        <v>-0.8450000000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0355</v>
+        <v>2.7375</v>
       </c>
       <c r="G9" t="n">
         <v>0.2698</v>
@@ -1156,13 +1156,13 @@
         <v>5.681</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.6876</v>
+        <v>-2.6422</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.6726</v>
+        <v>-1.3291</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.015</v>
+        <v>-1.3131</v>
       </c>
       <c r="V9" t="n">
         <v>3.1653</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. HINAREJOS GOMEZ</t>
+          <t>B. BREM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.081</v>
+        <v>1.8902</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6993</v>
+        <v>2.313000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7803</v>
+        <v>-0.4229000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0646</v>
+        <v>-5.6605</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6072</v>
+        <v>-2.0773</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.5421</v>
+        <v>-3.5833</v>
       </c>
       <c r="J10" t="n">
-        <v>5.0251</v>
+        <v>0.8419999999999995</v>
       </c>
       <c r="K10" t="n">
-        <v>6.1305</v>
+        <v>4.0715</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1055</v>
+        <v>-3.229500000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.9604</v>
+        <v>-6.5028</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5235</v>
+        <v>-6.1487</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4368</v>
+        <v>-0.3539999999999998</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5655</v>
+        <v>5.4977</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.4978</v>
+        <v>-2.9322</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9323</v>
+        <v>8.4298</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4303</v>
+        <v>-0.8027</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6379</v>
+        <v>-0.04180000000000006</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2077</v>
+        <v>-0.761</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.01029999999999998</v>
+        <v>2.8558</v>
       </c>
       <c r="W10" t="n">
-        <v>2.534</v>
+        <v>4.4448</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5443</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. BREM</t>
+          <t>J. VILLARROYA FELIPO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7845</v>
+        <v>1.2351</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1828999999999991</v>
+        <v>0.4683</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9675</v>
+        <v>0.7667</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.6605</v>
+        <v>0.9142</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0773</v>
+        <v>1.0007</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.5833</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8419999999999995</v>
+        <v>0.4502</v>
       </c>
       <c r="K11" t="n">
-        <v>4.0715</v>
+        <v>1.0496</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.229500000000001</v>
+        <v>-0.5994</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.5028</v>
+        <v>0.464</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.1487</v>
+        <v>-0.0489</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3539999999999998</v>
+        <v>0.5128</v>
       </c>
       <c r="P11" t="n">
-        <v>5.4977</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9322</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>8.4298</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.4776</v>
+        <v>0.3209</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.1717</v>
+        <v>0.0181</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.3059</v>
+        <v>0.3028</v>
       </c>
       <c r="V11" t="n">
-        <v>2.8558</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>4.4448</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>A. SEMEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9772</v>
+        <v>1.1292</v>
       </c>
       <c r="E12" t="n">
-        <v>6.6316</v>
+        <v>0.202</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.608600000000001</v>
+        <v>0.9273</v>
       </c>
       <c r="G12" t="n">
-        <v>5.012100000000001</v>
+        <v>1.1292</v>
       </c>
       <c r="H12" t="n">
-        <v>8.493400000000001</v>
+        <v>0.7351</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.4814</v>
+        <v>0.3942</v>
       </c>
       <c r="J12" t="n">
-        <v>20.0508</v>
+        <v>1.082</v>
       </c>
       <c r="K12" t="n">
-        <v>18.5576</v>
+        <v>1.0404</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4932</v>
+        <v>0.0417</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.0389</v>
+        <v>0.0472</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.0639</v>
+        <v>-0.3053</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.9748</v>
+        <v>0.3525</v>
       </c>
       <c r="P12" t="n">
-        <v>8.246499999999999</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q12" t="n">
-        <v>-27.6721</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>35.9185</v>
+        <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.556</v>
+        <v>0.1833</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3638</v>
+        <v>0.0362</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.192500000000001</v>
+        <v>0.1471</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.6797</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>16.6159</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-21.2957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. CASARES FALAGUERA</t>
+          <t>H. HINAREJOS GOMEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3943</v>
+        <v>-1.1853</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8273</v>
+        <v>2.0952</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4329999999999998</v>
+        <v>-3.2806</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2829</v>
+        <v>1.0646</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2186000000000001</v>
+        <v>4.6072</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06429999999999991</v>
+        <v>-3.5421</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5544</v>
+        <v>5.0251</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5544</v>
+        <v>6.1305</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-1.1055</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2715</v>
+        <v>-3.9604</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3358</v>
+        <v>-1.5235</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.06429999999999991</v>
+        <v>-2.4368</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0995</v>
+        <v>-2.5655</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>-5.4978</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7331</v>
+        <v>2.9323</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6796</v>
+        <v>0.326</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4404</v>
+        <v>0.03400000000000003</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2392</v>
+        <v>0.2919</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3324</v>
+        <v>-0.01029999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.534</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3324</v>
+        <v>-2.5443</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. BOYENZA</t>
+          <t>F. CASARES FALAGUERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.7631</v>
+        <v>-2.1773</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4875</v>
+        <v>-2.635</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2756</v>
+        <v>0.4578</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8357</v>
+        <v>-0.2829</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7395</v>
+        <v>-0.2186000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9037999999999999</v>
+        <v>-0.06429999999999991</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2101</v>
+        <v>-0.5544</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0433</v>
+        <v>-0.5544</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0457</v>
+        <v>0.2715</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7828</v>
+        <v>0.3358</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7371000000000001</v>
+        <v>-0.06429999999999991</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0996</v>
+        <v>0.7331</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1117</v>
+        <v>-0.4624</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2187</v>
+        <v>-0.2481</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1071</v>
+        <v>-0.2143</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.2224</v>
+        <v>-0.3324</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2224</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.9911</v>
+        <v>-2.4858</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4408</v>
+        <v>-0.3857000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5504</v>
+        <v>-2.1001</v>
       </c>
       <c r="G15" t="n">
         <v>-2.4139</v>
@@ -1624,13 +1624,13 @@
         <v>2.7489</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2264999999999999</v>
+        <v>0.2789</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4367000000000001</v>
+        <v>0.4917000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6633</v>
+        <v>-0.2127</v>
       </c>
       <c r="V15" t="n">
         <v>-1.267</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JODAR SAIZ</t>
+          <t>S. BOYENZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.669</v>
+        <v>-2.9662</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8502</v>
+        <v>-0.6659</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8188</v>
+        <v>-2.3003</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.7279</v>
+        <v>-0.8357</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9519</v>
+        <v>-1.7395</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7761</v>
+        <v>0.9037999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.971</v>
+        <v>0.2101</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2785</v>
+        <v>0.0433</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6926</v>
+        <v>0.1667</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.6989</v>
+        <v>-1.0457</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2303</v>
+        <v>-1.7828</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4687</v>
+        <v>0.7371000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9321</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1991</v>
+        <v>1.0996</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2632</v>
+        <v>-0.09140000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2111</v>
+        <v>0.04039999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0519</v>
+        <v>-0.1318</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.945</v>
+        <v>-2.2224</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.267</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>J. JODAR SAIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.832399999999999</v>
+        <v>-5.1025</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5975</v>
+        <v>-2.5067</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2347</v>
+        <v>-2.5958</v>
       </c>
       <c r="G17" t="n">
-        <v>22.2772</v>
+        <v>-2.7279</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.036600000000001</v>
+        <v>-0.9519</v>
       </c>
       <c r="I17" t="n">
-        <v>27.3138</v>
+        <v>-1.7761</v>
       </c>
       <c r="J17" t="n">
-        <v>37.9417</v>
+        <v>0.971</v>
       </c>
       <c r="K17" t="n">
-        <v>7.4172</v>
+        <v>0.2785</v>
       </c>
       <c r="L17" t="n">
-        <v>30.5244</v>
+        <v>0.6926</v>
       </c>
       <c r="M17" t="n">
-        <v>-15.6643</v>
+        <v>-3.6989</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.4536</v>
+        <v>-1.2303</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.2106</v>
+        <v>-2.4687</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.7803</v>
+        <v>-0.733</v>
       </c>
       <c r="Q17" t="n">
-        <v>-36.2852</v>
+        <v>-2.9321</v>
       </c>
       <c r="R17" t="n">
-        <v>29.5043</v>
+        <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>-16.8615</v>
+        <v>-0.6966</v>
       </c>
       <c r="T17" t="n">
-        <v>-13.4765</v>
+        <v>-0.8676999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.3854</v>
+        <v>0.1711</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.4677</v>
+        <v>-0.945</v>
       </c>
       <c r="W17" t="n">
-        <v>9.222</v>
+        <v>0.3219</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.6897</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>-11.8359</v>
+        <v>-8.2669</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.8408</v>
+        <v>-12.3295</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0051</v>
+        <v>4.0626</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8258</v>
@@ -1858,13 +1858,13 @@
         <v>6.047599999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.24</v>
+        <v>-3.6712</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.2331</v>
+        <v>-1.7217</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.0069</v>
+        <v>-1.9497</v>
       </c>
       <c r="V18" t="n">
         <v>0.6126</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. HYLLA</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>-14.9452</v>
+        <v>-13.9402</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.2924</v>
+        <v>-5.4724</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3472000000000011</v>
+        <v>-8.467700000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-11.3494</v>
+        <v>-5.494899999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.2386</v>
+        <v>-0.9749</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.1108</v>
+        <v>-4.5199</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.638500000000001</v>
+        <v>0.1475</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1914</v>
+        <v>1.269</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.4476</v>
+        <v>-1.1214</v>
       </c>
       <c r="M19" t="n">
-        <v>-7.710700000000001</v>
+        <v>-5.6424</v>
       </c>
       <c r="N19" t="n">
-        <v>-5.047</v>
+        <v>-2.2439</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.6635</v>
+        <v>-3.3985</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0995</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q19" t="n">
-        <v>-15.9436</v>
+        <v>-4.7646</v>
       </c>
       <c r="R19" t="n">
-        <v>17.0431</v>
+        <v>3.2986</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1437</v>
+        <v>0.3111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4772</v>
+        <v>-0.5436</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6664</v>
+        <v>0.8548</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.5517</v>
+        <v>-7.2903</v>
       </c>
       <c r="W19" t="n">
-        <v>4.7668</v>
+        <v>-0.3115</v>
       </c>
       <c r="X19" t="n">
-        <v>-8.3186</v>
+        <v>-6.9787</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>L. HYLLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>-15.1462</v>
+        <v>-14.4326</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.1043</v>
+        <v>-15.8958</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.0419</v>
+        <v>1.4634</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.494899999999999</v>
+        <v>-11.3494</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9749</v>
+        <v>-6.2386</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.5199</v>
+        <v>-5.1108</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1475</v>
+        <v>-3.638500000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.269</v>
+        <v>-1.1914</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1214</v>
+        <v>-2.4476</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.6424</v>
+        <v>-7.710700000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2439</v>
+        <v>-5.047</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.3985</v>
+        <v>-2.6635</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.7646</v>
+        <v>-15.9436</v>
       </c>
       <c r="R20" t="n">
-        <v>3.2986</v>
+        <v>17.0431</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.895</v>
+        <v>-0.6309999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1757</v>
+        <v>-1.0805</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2806000000000001</v>
+        <v>0.4494999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-7.2903</v>
+        <v>-3.5517</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3115</v>
+        <v>4.7668</v>
       </c>
       <c r="X20" t="n">
-        <v>-6.9787</v>
+        <v>-8.3186</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>-20.1301</v>
+        <v>-17.4489</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.3269</v>
+        <v>-12.307</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.8033</v>
+        <v>-5.141800000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-6.9279</v>
@@ -2092,13 +2092,13 @@
         <v>16.31</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.7073</v>
+        <v>-1.0258</v>
       </c>
       <c r="T21" t="n">
-        <v>-3.9931</v>
+        <v>-1.9731</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2859</v>
+        <v>0.9474</v>
       </c>
       <c r="V21" t="n">
         <v>0.2178</v>
@@ -2125,13 +2125,13 @@
         <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>-34.5514</v>
+        <v>-28.8766</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.2448</v>
+        <v>-5.795</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.3067</v>
+        <v>-23.0819</v>
       </c>
       <c r="G22" t="n">
         <v>-9.5618</v>
@@ -2170,13 +2170,13 @@
         <v>40.4999</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.8883</v>
+        <v>-2.2135</v>
       </c>
       <c r="T22" t="n">
-        <v>-7.3352</v>
+        <v>-3.8854</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5531999999999999</v>
+        <v>1.6716</v>
       </c>
       <c r="V22" t="n">
         <v>-15.0851</v>
@@ -2203,13 +2203,13 @@
         <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.013400000000001</v>
+        <v>24.86519999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>7.755499999999982</v>
+        <v>16.8381</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.7686</v>
+        <v>8.026900000000005</v>
       </c>
       <c r="G23" t="n">
         <v>64.9541</v>
@@ -2218,10 +2218,10 @@
         <v>67.86259999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9086</v>
+        <v>-2.908599999999998</v>
       </c>
       <c r="J23" t="n">
-        <v>287.4001999999999</v>
+        <v>287.4002</v>
       </c>
       <c r="K23" t="n">
         <v>208.4967</v>
@@ -2239,22 +2239,22 @@
         <v>-81.81319999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-53.1448</v>
+        <v>-53.14479999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-434.3214</v>
+        <v>-434.3213999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>381.1755999999999</v>
+        <v>381.1756</v>
       </c>
       <c r="S23" t="n">
-        <v>-40.8875</v>
+        <v>-10.0082</v>
       </c>
       <c r="T23" t="n">
-        <v>-37.4209</v>
+        <v>-28.337</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.467499999999999</v>
+        <v>18.3275</v>
       </c>
       <c r="V23" t="n">
         <v>23.06490000000001</v>
